--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2598,7 +2598,7 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="269">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -533,7 +533,7 @@
 </t>
   </si>
   <si>
-    <t>Kind of organization</t>
+    <t>Cadre d'exercice</t>
   </si>
   <si>
     <t>The kind(s) of organization that this is.</t>
@@ -547,13 +547,10 @@
     <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Used to categorize the organization.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1188,7 +1185,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.10546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="105.80859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -2649,11 +2646,9 @@
       <c r="X13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -2686,24 +2681,24 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>176</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2726,19 +2721,19 @@
         <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>76</v>
@@ -2787,7 +2782,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2802,13 +2797,13 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>76</v>
@@ -2816,10 +2811,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2842,19 +2837,19 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -2903,7 +2898,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2921,7 +2916,7 @@
         <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
@@ -2932,10 +2927,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2958,19 +2953,19 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3019,7 +3014,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3028,19 +3023,19 @@
         <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AJ16" t="s" s="2">
+      <c r="AK16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AL16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>76</v>
@@ -3048,10 +3043,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3074,19 +3069,19 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3135,7 +3130,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3144,19 +3139,19 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AJ17" t="s" s="2">
+      <c r="AK17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>76</v>
@@ -3164,10 +3159,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3190,17 +3185,17 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3249,7 +3244,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3267,10 +3262,10 @@
         <v>160</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>76</v>
@@ -3278,10 +3273,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3304,19 +3299,19 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3365,7 +3360,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3383,7 +3378,7 @@
         <v>76</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>76</v>
@@ -3394,10 +3389,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3420,13 +3415,13 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3477,7 +3472,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3495,7 +3490,7 @@
         <v>76</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>76</v>
@@ -3506,10 +3501,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3538,7 +3533,7 @@
         <v>133</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>135</v>
@@ -3591,7 +3586,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3609,7 +3604,7 @@
         <v>76</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>76</v>
@@ -3620,14 +3615,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3649,10 +3644,10 @@
         <v>132</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>135</v>
@@ -3707,7 +3702,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3736,10 +3731,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3765,14 +3760,14 @@
         <v>165</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -3797,14 +3792,14 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="Y23" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="Y23" t="s" s="2">
+      <c r="Z23" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="Z23" t="s" s="2">
-        <v>244</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>76</v>
       </c>
@@ -3821,7 +3816,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3839,7 +3834,7 @@
         <v>76</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -3850,10 +3845,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3876,17 +3871,17 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -3935,7 +3930,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3950,10 +3945,10 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>76</v>
@@ -3964,10 +3959,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3990,17 +3985,17 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4049,7 +4044,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4064,10 +4059,10 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>76</v>
@@ -4078,10 +4073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4104,17 +4099,17 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4163,7 +4158,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4178,10 +4173,10 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4192,10 +4187,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4218,17 +4213,17 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4277,7 +4272,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4295,7 +4290,7 @@
         <v>76</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>76</v>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Organization-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
